--- a/QCM4_5_PHY.xlsx
+++ b/QCM4_5_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A77766-ED31-4C67-BF8A-C3D4D4565E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F83E198-C892-4CCC-AB73-7A5E079D34BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="119">
   <si>
     <t>Question</t>
   </si>
@@ -286,98 +286,107 @@
     <t>Lorsque la pierre touche le sol, la vitesse du système vaut :</t>
   </si>
   <si>
+    <t>$v_B = \sqrt{6}\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$v_B = 2\sqrt{6}\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$v_B = 3\sqrt{6}\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$V_B = 5\sqrt{6}\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$F_R = 4,5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$F_R = 5,5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$F_R = 5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$F_R = 6,0\text{ N}$</t>
+  </si>
+  <si>
+    <t>II. La portion BC est rectiligne et rugueuse et vaut $L = 2\text{ m}$. On assimilera les forces de frottement à une force unique $f$ constante et opposée au mouvement. Sachant que la vitesse en C vaut $V_C = 2\text{ m.s}^{-1}$, la valeur de la force de frottement sur la portion BC vaut :</t>
+  </si>
+  <si>
+    <t>$f = 0,375\text{ N}$</t>
+  </si>
+  <si>
+    <t>$f = 0,750\text{ N}$</t>
+  </si>
+  <si>
+    <t>$f = 1,505\text{ N}$</t>
+  </si>
+  <si>
+    <t>$f = 3,10\text{ N}$</t>
+  </si>
+  <si>
+    <t>$2,5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$10\text{ N}$</t>
+  </si>
+  <si>
+    <t>$20\text{ N}$</t>
+  </si>
+  <si>
+    <t>$20\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$102,5\text{ J}$</t>
+  </si>
+  <si>
+    <t>La vitesse du mobile M en B vaut :</t>
+  </si>
+  <si>
+    <t>Par application de la deuxième loi de Newton au mobile M en mouvement par rapport au repère fixe cartésien d'origine O et en projetant l'équation vectorielle obtenue dans la base de Frenet, déterminer l'intensité de la force de réaction $\vec{R}$ de la piste sur le mobile en B :</t>
+  </si>
+  <si>
+    <t>La valeur de la force de frottement sur la portion BC vaut :</t>
+  </si>
+  <si>
+    <t>Déterminer l'intensité minimale à donner à $\vec{F}$ pour que le projectile M s'arrête sur la piste en D :</t>
+  </si>
+  <si>
+    <t>On suppose que la force est égale maintenant à $102,5\text{ N}$. La valeur numérique de la vitesse $V_D$ au point D où il quitte la piste en D est plus proche de :</t>
+  </si>
+  <si>
+    <t>L'énergie mécanique $E_m$ du projectile en D vaut :</t>
+  </si>
+  <si>
     <t>La trajectoire OAMNB : Un corps solide (S) de masse $m = 200\text{ g}$ assimilable à un point matériel est en mouvement sur une trajectoire OAMNB constitué de deux parties. Le mouvement de (S) se fait avec frottement uniquement sur la partie OA. 
-&lt;img src="/images/PHY_QCM1_4_Q11.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 La partie OA rectiligne horizontale de longueur $OA = 80\text{ cm}$. La partie AMNB circulaire de centre C est de rayon $r = 50\text{ cm}$. A l'instant $t = 0$ le corps (S) est envoyé du point O (origine des espaces) avec une vitesse $v_0 = 2\text{ m/s}$, il atteint le point A avec une vitesse nulle ($v_A = 0$), et poursuit son mouvement sur la partie AMNB. Donnée : $g = 10\text{ m.s}^{-2}$.</t>
   </si>
   <si>
-    <t>$v_B = \sqrt{6}\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$v_B = 2\sqrt{6}\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$v_B = 3\sqrt{6}\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$V_B = 5\sqrt{6}\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$F_R = 4,5\text{ N}$</t>
-  </si>
-  <si>
-    <t>$F_R = 5,5\text{ N}$</t>
-  </si>
-  <si>
-    <t>$F_R = 5\text{ N}$</t>
-  </si>
-  <si>
-    <t>$F_R = 6,0\text{ N}$</t>
-  </si>
-  <si>
-    <t>II. La portion BC est rectiligne et rugueuse et vaut $L = 2\text{ m}$. On assimilera les forces de frottement à une force unique $f$ constante et opposée au mouvement. Sachant que la vitesse en C vaut $V_C = 2\text{ m.s}^{-1}$, la valeur de la force de frottement sur la portion BC vaut :</t>
-  </si>
-  <si>
-    <t>$f = 0,375\text{ N}$</t>
-  </si>
-  <si>
-    <t>$f = 0,750\text{ N}$</t>
-  </si>
-  <si>
-    <t>$f = 1,505\text{ N}$</t>
-  </si>
-  <si>
-    <t>$f = 3,10\text{ N}$</t>
-  </si>
-  <si>
-    <t>$2,5\text{ N}$</t>
-  </si>
-  <si>
-    <t>$5\text{ N}$</t>
-  </si>
-  <si>
-    <t>$10\text{ N}$</t>
-  </si>
-  <si>
-    <t>$20\text{ N}$</t>
-  </si>
-  <si>
-    <t>$20\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$102,5\text{ J}$</t>
-  </si>
-  <si>
-    <t>La vitesse du mobile M en B vaut :</t>
-  </si>
-  <si>
-    <t>Par application de la deuxième loi de Newton au mobile M en mouvement par rapport au repère fixe cartésien d'origine O et en projetant l'équation vectorielle obtenue dans la base de Frenet, déterminer l'intensité de la force de réaction $\vec{R}$ de la piste sur le mobile en B :</t>
-  </si>
-  <si>
-    <t>La valeur de la force de frottement sur la portion BC vaut :</t>
-  </si>
-  <si>
-    <t>Déterminer l'intensité minimale à donner à $\vec{F}$ pour que le projectile M s'arrête sur la piste en D :</t>
-  </si>
-  <si>
-    <t>On suppose que la force est égale maintenant à $102,5\text{ N}$. La valeur numérique de la vitesse $V_D$ au point D où il quitte la piste en D est plus proche de :</t>
-  </si>
-  <si>
-    <t>L'énergie mécanique $E_m$ du projectile en D vaut :</t>
+    <t xml:space="preserve">Une piste ABC : Un mobile M de masse $m = 150\text{ g}$, supposé ponctuel, peut glisser le long d'une piste ABC dont la forme est donnée par la figure ci-après ; Le mouvement a lieu dans un plan vertical. I. La partie curviligne est un quart de cercle de rayon $r = 1\text{ m}$, parfaitement lisse de telle sorte que les forces de frottement y sont négligeables. Le mobile M est lancé en A avec une vitesse $v_A = 2\text{ m.s}^{-1}$ verticale et dirigée vers le bas. Il est repéré à l'instant $t$ par l'angle $\theta$.
+</t>
+  </si>
+  <si>
+    <t>La piste ABCD : La piste de lancement d'un projectile M comprend une partie rectiligne horizontale ABC et une portion circulaire CD centrée en O, de rayon $R = 1\text{ m}$, d'angle au centre O, $\alpha = 60^\circ$ est telle que OC soit perpendiculaire à AC. On suppose qu'il n'y a pas de forces de frottement exercées par la piste sur le mobile tout le long du trajet parcouru par ce dernier. Le projectile M assimilable à un point de masse $m = 0,5\text{ kg}$, est lancé à partir du point A sans vitesse initiale suivant AB de longueur $1\text{ m}$ avec une force constante $\vec{F}$, horizontale et s'exerçant qu'entre A et B. 
+On donne $g = 10\text{ m.s}^{-2}$ on suppose que l'origine de l'énergie potentielle du mobile M est le niveau horizontal de la piste.</t>
   </si>
   <si>
     <t>Une benne : Une benne transporte un objet de masse $m$ positionné comme indiqué sur la figure ci-dessous. La benne se soulève à vitesse constante et au bout de 30 secondes, l'objet se met à glisser et le chauffeur arrête immédiatement la benne. L'angle entre le plancher de la benne et l'horizontal est alors $\alpha = 30^\circ$. 
-&lt;img src="/images/PHY_QCM1_4_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 On donne : $\sin(30^\circ) = 0,5 ; \cos(30^\circ) = 0,8 ; \tan(30^\circ) = 0,5 ; g = 10\text{ m.s}^{-2}$. La force de frottement statique quand elle est maximale s'exprime $f_{max} = k_{sta}.R$, $R$ réaction entre le plancher et l'objet.</t>
   </si>
   <si>
-    <t>La piste ABCD : La piste de lancement d'un projectile M comprend une partie rectiligne horizontale ABC et une portion circulaire CD centrée en O, de rayon $R = 1\text{ m}$, d'angle au centre O, $\alpha = 60^\circ$ est telle que OC soit perpendiculaire à AC. On suppose qu'il n'y a pas de forces de frottement exercées par la piste sur le mobile tout le long du trajet parcouru par ce dernier. Le projectile M assimilable à un point de masse $m = 0,5\text{ kg}$, est lancé à partir du point A sans vitesse initiale suivant AB de longueur $1\text{ m}$ avec une force constante $\vec{F}$, horizontale et s'exerçant qu'entre A et B. 
-&lt;img src="/images/PHY_QCM1_4_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-On donne $g = 10\text{ m.s}^{-2}$ on suppose que l'origine de l'énergie potentielle du mobile M est le niveau horizontal de la piste.</t>
-  </si>
-  <si>
-    <t>Une piste ABC : Un mobile M de masse $m = 150\text{ g}$, supposé ponctuel, peut glisser le long d'une piste ABC dont la forme est donnée par la figure ci-après ; Le mouvement a lieu dans un plan vertical. I. La partie curviligne est un quart de cercle de rayon $r = 1\text{ m}$, parfaitement lisse de telle sorte que les forces de frottement y sont négligeables. Le mobile M est lancé en A avec une vitesse $v_A = 2\text{ m.s}^{-1}$ verticale et dirigée vers le bas. Il est repéré à l'instant $t$ par l'angle $\theta$.
-&lt;img src="/images/PHY_QCM1_4_Q12.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+    <t>PHY_QCM1_4_Q11.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q12.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q13.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q14.png</t>
   </si>
 </sst>
 </file>
@@ -1010,9 +1019,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>52</v>
@@ -1035,6 +1044,9 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1131,114 +1143,120 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="153" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
+      </c>
+      <c r="J11" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="242.25" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>113</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="J14" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
@@ -1249,12 +1267,12 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
@@ -1265,12 +1283,12 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="178.5" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="153" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>57</v>
@@ -1296,8 +1314,11 @@
       <c r="I17" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
@@ -1326,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
         <v>59</v>
       </c>
@@ -1352,7 +1373,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>60</v>
       </c>

--- a/QCM4_5_PHY.xlsx
+++ b/QCM4_5_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F83E198-C892-4CCC-AB73-7A5E079D34BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96E98EA-AF06-4432-A5EE-68EC1883AB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="123">
   <si>
     <t>Question</t>
   </si>
@@ -66,9 +66,6 @@
     <t>$2\text{ m.s}^{-2}$</t>
   </si>
   <si>
-    <t>Autre</t>
-  </si>
-  <si>
     <t>$3\text{ m.s}^{-2}$</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>$\cos\alpha_m = \frac{2}{3}$</t>
   </si>
   <si>
-    <t>$\cos\alpha_m = -\frac{2}{3}$</t>
-  </si>
-  <si>
     <t>$k_{sta} = 0$</t>
   </si>
   <si>
@@ -141,15 +135,6 @@
     <t>$k_{sta} \simeq 0,5$</t>
   </si>
   <si>
-    <t>$k_{sta} = 1,7$</t>
-  </si>
-  <si>
-    <t>$k_{sta} = 1$</t>
-  </si>
-  <si>
-    <t>L'objet ne s'arrête pas et glisse avec une accélération uniforme et se déplace de $2\text{ m}$ en $2\text{ s}$ jusqu'au bout de la benne fermée. Cette accélération est due à la différence entre la gravitation et la force de frottement dynamique qui s'exprime $f_{dyn} = k_{dyn}.R$.</t>
-  </si>
-  <si>
     <t>$2,5\text{ m.s}^{-2}$</t>
   </si>
   <si>
@@ -183,12 +168,6 @@
     <t>$k_{dyn} = 1$</t>
   </si>
   <si>
-    <t>Le travail de la réaction R lors du déplacement OA est :</t>
-  </si>
-  <si>
-    <t>L'intensité de la force de frottement est :</t>
-  </si>
-  <si>
     <t>L'équation horaire $x(t)$ du mouvement de S le long de la trajectoire OA est :</t>
   </si>
   <si>
@@ -201,9 +180,6 @@
     <t>Le coefficient de frottement statique entre le plancher de la benne et l'objet est :</t>
   </si>
   <si>
-    <t>L'accélération de l'objet est de :</t>
-  </si>
-  <si>
     <t>Le coefficient de frottement dynamique lors de l'accélération de l'objet est :</t>
   </si>
   <si>
@@ -234,19 +210,6 @@
     <t>énergie cinétique</t>
   </si>
   <si>
-    <t>mécanique</t>
-  </si>
-  <si>
-    <t>électrique</t>
-  </si>
-  <si>
-    <t>autre répons,</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Chute libre&lt;/b&gt;&lt;/center&gt;
-On lâche une pierre, de masse m = 100 g, du haut d'un immeuble de hauteur h = 20 m On néglige toutes les forces dues à l'air. Pour cette étude, on choisit un axe vertical orienté vers le bas, l'origine de l'axe étant confondu avec l'origine du mouvement. On donne g = 10 m.s-2 .</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Lors de la chute, l'énergie cinétique du système se transforme en  :</t>
   </si>
   <si>
@@ -310,9 +273,6 @@
     <t>$F_R = 6,0\text{ N}$</t>
   </si>
   <si>
-    <t>II. La portion BC est rectiligne et rugueuse et vaut $L = 2\text{ m}$. On assimilera les forces de frottement à une force unique $f$ constante et opposée au mouvement. Sachant que la vitesse en C vaut $V_C = 2\text{ m.s}^{-1}$, la valeur de la force de frottement sur la portion BC vaut :</t>
-  </si>
-  <si>
     <t>$f = 0,375\text{ N}$</t>
   </si>
   <si>
@@ -331,12 +291,6 @@
     <t>$5\text{ N}$</t>
   </si>
   <si>
-    <t>$10\text{ N}$</t>
-  </si>
-  <si>
-    <t>$20\text{ N}$</t>
-  </si>
-  <si>
     <t>$20\text{ m.s}^{-1}$</t>
   </si>
   <si>
@@ -346,47 +300,119 @@
     <t>La vitesse du mobile M en B vaut :</t>
   </si>
   <si>
-    <t>Par application de la deuxième loi de Newton au mobile M en mouvement par rapport au repère fixe cartésien d'origine O et en projetant l'équation vectorielle obtenue dans la base de Frenet, déterminer l'intensité de la force de réaction $\vec{R}$ de la piste sur le mobile en B :</t>
-  </si>
-  <si>
-    <t>La valeur de la force de frottement sur la portion BC vaut :</t>
-  </si>
-  <si>
     <t>Déterminer l'intensité minimale à donner à $\vec{F}$ pour que le projectile M s'arrête sur la piste en D :</t>
   </si>
   <si>
-    <t>On suppose que la force est égale maintenant à $102,5\text{ N}$. La valeur numérique de la vitesse $V_D$ au point D où il quitte la piste en D est plus proche de :</t>
-  </si>
-  <si>
     <t>L'énergie mécanique $E_m$ du projectile en D vaut :</t>
   </si>
   <si>
-    <t>La trajectoire OAMNB : Un corps solide (S) de masse $m = 200\text{ g}$ assimilable à un point matériel est en mouvement sur une trajectoire OAMNB constitué de deux parties. Le mouvement de (S) se fait avec frottement uniquement sur la partie OA. 
-La partie OA rectiligne horizontale de longueur $OA = 80\text{ cm}$. La partie AMNB circulaire de centre C est de rayon $r = 50\text{ cm}$. A l'instant $t = 0$ le corps (S) est envoyé du point O (origine des espaces) avec une vitesse $v_0 = 2\text{ m/s}$, il atteint le point A avec une vitesse nulle ($v_A = 0$), et poursuit son mouvement sur la partie AMNB. Donnée : $g = 10\text{ m.s}^{-2}$.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une piste ABC : Un mobile M de masse $m = 150\text{ g}$, supposé ponctuel, peut glisser le long d'une piste ABC dont la forme est donnée par la figure ci-après ; Le mouvement a lieu dans un plan vertical. I. La partie curviligne est un quart de cercle de rayon $r = 1\text{ m}$, parfaitement lisse de telle sorte que les forces de frottement y sont négligeables. Le mobile M est lancé en A avec une vitesse $v_A = 2\text{ m.s}^{-1}$ verticale et dirigée vers le bas. Il est repéré à l'instant $t$ par l'angle $\theta$.
+    <t>PHY_QCM1_4_Q11.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q12.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q13.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q14.png</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Chute libre&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On lâche une pierre, de masse m = 100 g, du haut d'un immeuble de hauteur h = 20 m. On néglige toutes les forces dues à l'air. Pour cette étude, on choisit un axe vertical orienté vers le bas, l'origine de l'axe étant confondu avec l'origine du mouvement. On donne g = 10 m.s-2 .</t>
+  </si>
+  <si>
+    <t>énergie mécanique</t>
+  </si>
+  <si>
+    <t>énergie électrique</t>
+  </si>
+  <si>
+    <t>autre réponse</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La trajectoire OAMNB : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un corps solide (S) de masse $m = 200\text{ g}$ assimilable à un point matériel est en mouvement sur une trajectoire OAMNB constitué de deux parties. Le mouvement de (S) se fait avec frottement uniquement sur la partie OA. 
+&lt;br&gt;* La partie OA rectiligne horizontale de longueur $OA = 80\text{ cm}$. 
+&lt;br&gt; * La partie AMNB circulaire de centre C est de rayon $r = 50\text{ cm}$. 
+A l'instant $t = 0$ le corps (S) est envoyé du point O (origine des espaces) avec une vitesse $v_0 = 2\text{ m/s}$, il atteint le point A avec une vitesse nulle ($v_A = 0$), et poursuit son mouvement sur la partie AMNB. 
+Donnée : $g = 10\text{ m.s}^{-2}$.</t>
+  </si>
+  <si>
+    <t>Le travail de la réaction $\vecR$ lors du déplacement OA est :</t>
+  </si>
+  <si>
+    <t>$W_{OA}(\vec{R}) = 4\text{ J}$</t>
+  </si>
+  <si>
+    <t>L'intensité f de la force de frottement est :</t>
+  </si>
+  <si>
+    <t>$\cos\alpha_m = \frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>$\alpha_m = 45°$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Une piste ABC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un mobile M de masse $m = 150\text{ g}$, supposé ponctuel, peut glisser le long d'une piste ABC dont la forme est donnée par la figure ci-après ; Le mouvement a lieu dans un plan vertical.
+ I. La partie curviligne est un quart de cercle de rayon $r = 1\text{ m}$, parfaitement lisse de telle sorte que les forces de frottement y sont négligeables. Le mobile M est lancé en A avec une vitesse $v_A = 2\text{ m.s}^{-1}$ verticale et dirigée vers le bas. Il est repéré à l'instant $t$ par l'angle $\theta$.
 </t>
   </si>
   <si>
-    <t>La piste ABCD : La piste de lancement d'un projectile M comprend une partie rectiligne horizontale ABC et une portion circulaire CD centrée en O, de rayon $R = 1\text{ m}$, d'angle au centre O, $\alpha = 60^\circ$ est telle que OC soit perpendiculaire à AC. On suppose qu'il n'y a pas de forces de frottement exercées par la piste sur le mobile tout le long du trajet parcouru par ce dernier. Le projectile M assimilable à un point de masse $m = 0,5\text{ kg}$, est lancé à partir du point A sans vitesse initiale suivant AB de longueur $1\text{ m}$ avec une force constante $\vec{F}$, horizontale et s'exerçant qu'entre A et B. 
-On donne $g = 10\text{ m.s}^{-2}$ on suppose que l'origine de l'énergie potentielle du mobile M est le niveau horizontal de la piste.</t>
-  </si>
-  <si>
-    <t>Une benne : Une benne transporte un objet de masse $m$ positionné comme indiqué sur la figure ci-dessous. La benne se soulève à vitesse constante et au bout de 30 secondes, l'objet se met à glisser et le chauffeur arrête immédiatement la benne. L'angle entre le plancher de la benne et l'horizontal est alors $\alpha = 30^\circ$. 
-On donne : $\sin(30^\circ) = 0,5 ; \cos(30^\circ) = 0,8 ; \tan(30^\circ) = 0,5 ; g = 10\text{ m.s}^{-2}$. La force de frottement statique quand elle est maximale s'exprime $f_{max} = k_{sta}.R$, $R$ réaction entre le plancher et l'objet.</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q11.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q12.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q13.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_4_Q14.png</t>
+    <t>Par application de la deuxième loi de Newton au mobile M en mouvement par rapport au repère fixe cartésien d'origine O et en projetant l'équation vectorielle obtenue dans la base de Frenet, déterminer l'intensité de la force de réaction $\vec{F_R}$ de la piste sur le mobile en B :</t>
+  </si>
+  <si>
+    <t>$F_R = 5,1\text{ N}$</t>
+  </si>
+  <si>
+    <t>II. La portion BC est rectiligne et rugueuse et vaut $L = 2\text{ m}$. On assimilera les forces de frottement à une force unique $f$ constante et opposée au mouvement. Sachant que la vitesse en C vaut $V_C = 2\text{ m.s}^{-1}$, La valeur de la force de frottement sur la portion BC vaut :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La piste ABCD : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;La piste de lancement d'un projectile M comprend une partie rectiligne horizontale ABC et une portion circulaire CD centrée en O, de rayon $R = 1\text{ m}$, d'angle au centre O, $\alpha = 60^\circ$ est telle que OC soit perpendiculaire à AC. On suppose qu'il n'y a pas de forces de frottement exercées par la piste sur le mobile tout le long du trajet parcouru par ce dernier. 
+Le projectile M assimilable à un point de masse $m = 0,5\text{ kg}$, est lancé à partir du point A sans vitesse initiale suivant AB de longueur $1\text{ m}$ avec une force constante $\vec{F}$, horizontale et ne s'exerçant qu'entre A et B. 
+On donne:
+ $g = 10\text{ m.s}^{-2}$ 
+on suppose que l'origine de l'énergie potentielle du mobile M est le niveau horizontal de la piste.</t>
+  </si>
+  <si>
+    <t>$4,5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$1,25\text{ N}$</t>
+  </si>
+  <si>
+    <t>On suppose que la force $\vecF$ est égale maintenant à $102,5\text{ N}$. La valeur numérique de la vitesse $V_D$ avec laquelle le projectile M quitte la piste en D est plus proche de :</t>
+  </si>
+  <si>
+    <t>$10\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$25\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$15\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Une benne : &lt;/b&gt;&lt;/center&gt;br&gt;
+&lt;br&gt;Une benne transporte un objet de masse $m$ positionné comme indiqué sur la figure ci-dessous. La benne se soulève à vitesse constante et au bout de 30 secondes, l'objet se met à glisser et le chauffeur arrête immédiatement la benne. L'angle entre le plancher de la benne et l'horizontal est alors $\alpha = 30^\circ$. 
+&lt;br&gt;On donne : 
+$\sin(30^\circ) = 0,5 ; $\quad$ \cos(30^\circ) = 0,8 ; $\quad$ \tan(30^\circ) = \frac{5}{8} ; $\quad$ g = 10\text{ m.s}^{-2}$. 
+La force de frottement statique quand elle est maximale s'exprime $f_{max} = k_{sta}.R$, $R$ réaction entre le plancher et l'objet.</t>
+  </si>
+  <si>
+    <t>$k_{sta} \simeq 1$</t>
+  </si>
+  <si>
+    <t>$k_{sta} \simeq 1,7$</t>
+  </si>
+  <si>
+    <t>L'objet ne s'arrête pas et glisse avec une accélération uniforme et se déplace de $2\text{ m}$ en $2\text{ s}$ jusqu'au bout de la benne fermée. Cette accélération est due à la différence entre la gravitation et la force de frottement dynamique qui s'exprime $f_{dyn} = k_{dyn}.R$.
+L'accélération de l'objet est de :</t>
+  </si>
+  <si>
+    <t>$1,5\text{ m.s}^{-2}$</t>
   </si>
 </sst>
 </file>
@@ -912,367 +938,375 @@
     </row>
     <row r="2" spans="1:11" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="153" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>94</v>
-      </c>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
@@ -1283,120 +1317,118 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="153" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="G17" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="G18" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="I18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/QCM4_5_PHY.xlsx
+++ b/QCM4_5_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96E98EA-AF06-4432-A5EE-68EC1883AB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B8106B-73F4-43F0-8102-0B3CB2CCA705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
   <si>
     <t>Question</t>
   </si>
@@ -81,9 +81,6 @@
     <t>$W_{OA}(\vec{R}) = -0,4\text{ J}$</t>
   </si>
   <si>
-    <t>$W_{OA}(\vec{R}) = 0\text{ J}$</t>
-  </si>
-  <si>
     <t>$W_{OA}(\vec{R}) = 0,4\text{ J}$</t>
   </si>
   <si>
@@ -265,9 +262,6 @@
   </si>
   <si>
     <t>$F_R = 5,5\text{ N}$</t>
-  </si>
-  <si>
-    <t>$F_R = 5\text{ N}$</t>
   </si>
   <si>
     <t>$F_R = 6,0\text{ N}$</t>
@@ -414,12 +408,21 @@
   <si>
     <t>$1,5\text{ m.s}^{-2}$</t>
   </si>
+  <si>
+    <t>$10,25\text{ J}$</t>
+  </si>
+  <si>
+    <t>$1,025\text{ J}$</t>
+  </si>
+  <si>
+    <t>$1025\text{ J}$</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,12 +443,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
       <name val="Consolas"/>
     </font>
   </fonts>
@@ -547,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -578,9 +575,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -938,119 +932,119 @@
     </row>
     <row r="2" spans="1:11" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="I2" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+        <v>54</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="F3" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>60</v>
+      <c r="I3" s="7" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="I4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
@@ -1062,37 +1056,37 @@
         <v>17</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>22</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
@@ -1101,261 +1095,269 @@
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13" t="s">
-        <v>88</v>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13" t="s">
-        <v>89</v>
+      <c r="D16" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="H17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>3</v>
@@ -1367,10 +1369,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>14</v>
@@ -1381,54 +1383,54 @@
     </row>
     <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>41</v>
-      </c>
       <c r="I19" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="I20" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
